--- a/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataWithBRCSpaceSystems.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WorkspaceDataWithBRCSpaceSystems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e302876\proph\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061FC8F9-3E13-493C-853D-6C5DEFFC9CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9092E267-DA95-4EC9-A776-BC8ED9C3BA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOE3 Pivot" sheetId="19" state="hidden" r:id="rId1"/>
@@ -51,10 +51,11 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId18"/>
-    <pivotCache cacheId="16" r:id="rId19"/>
-    <pivotCache cacheId="17" r:id="rId20"/>
+    <pivotCache cacheId="0" r:id="rId18"/>
+    <pivotCache cacheId="1" r:id="rId19"/>
+    <pivotCache cacheId="2" r:id="rId20"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -746,16 +747,16 @@
     <t>SAP Connection Enabled</t>
   </si>
   <si>
-    <t>Business Resource Code Description</t>
-  </si>
-  <si>
-    <t>Business Resource Code Type</t>
-  </si>
-  <si>
-    <t>Business Resource Code</t>
-  </si>
-  <si>
-    <t>Business Resource Code Segment Region</t>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>BRC Description</t>
+  </si>
+  <si>
+    <t>BRC Type</t>
+  </si>
+  <si>
+    <t>BRC Segment Region</t>
   </si>
 </sst>
 </file>
@@ -4232,7 +4233,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:N33" firstHeaderRow="1" firstDataRow="1" firstDataCol="14"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -4581,7 +4582,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Type">
   <location ref="A3:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="8"/>
   <pivotFields count="19">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -4790,7 +4791,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" missingCaption="_" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="BOE ID">
   <location ref="A3:T33" firstHeaderRow="1" firstDataRow="1" firstDataCol="20"/>
   <pivotFields count="20">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -8723,13 +8724,13 @@
         <v>142</v>
       </c>
       <c r="AG1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI1" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="AH1" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI1" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="AJ1" s="5" t="s">
         <v>11</v>
@@ -8907,10 +8908,10 @@
         <v>89</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
@@ -8941,28 +8942,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
-    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
-    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
-      <Value>2</Value>
-    </SipLabel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Custom Document" ma:contentTypeID="0x010100E6322E8F405D4D9EA89D8C83B7E1048B001BB96E1BE0ACBB41BF00782ED0412411" ma:contentTypeVersion="3" ma:contentTypeDescription="Custom Document" ma:contentTypeScope="" ma:versionID="3c14126572fa3c0d4c677ac1f3ba4426">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="D75E00DB-06CE-4005-B397-8C0860A4229B" xmlns:ns3="372b77af-8063-48a8-888c-73c0edf01dea" xmlns:ns4="d75e00db-06ce-4005-b397-8c0860a4229b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9e89026a025b72b85b9543506e7af3e1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
@@ -9065,32 +9044,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Unity_Description xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Unity_Tag xmlns="D75E00DB-06CE-4005-B397-8C0860A4229B" xsi:nil="true"/>
+    <Capabilities xmlns="d75e00db-06ce-4005-b397-8c0860a4229b" xsi:nil="true"/>
+    <SipLabel xmlns="372b77af-8063-48a8-888c-73c0edf01dea">
+      <Value>2</Value>
+    </SipLabel>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DE4120D-B400-435F-B862-B3B8683830A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9107,4 +9083,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2653FDDC-5C81-4B5A-A42F-7A63208AFFF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268822B0-DCAE-4D2C-8340-AB7554C48D72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="372b77af-8063-48a8-888c-73c0edf01dea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="D75E00DB-06CE-4005-B397-8C0860A4229B"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="d75e00db-06ce-4005-b397-8c0860a4229b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>